--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4195</v>
+        <v>4081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1239</v>
+        <v>1034</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28324</v>
+        <v>58118</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10179</v>
+        <v>6912</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2187</v>
+        <v>1861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>479</v>
+        <v>509</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H415"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4083,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5307,11 +5307,11 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5375,11 +5375,11 @@
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5409,11 +5409,11 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5443,11 +5443,11 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>20663</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5477,11 +5477,11 @@
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5511,11 +5511,11 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5545,11 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -7449,11 +7449,11 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8673,11 +8673,11 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9285,11 +9285,11 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10271,11 +10271,11 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10373,11 +10373,11 @@
         <v>1</v>
       </c>
       <c r="G284" t="n">
-        <v>670</v>
+        <v>0</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
         <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11121,11 +11121,11 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11189,11 +11189,11 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11223,11 +11223,11 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11291,11 +11291,11 @@
         <v>1</v>
       </c>
       <c r="G311" t="n">
-        <v>0</v>
+        <v>981</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11903,11 +11903,11 @@
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>843</v>
+        <v>0</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11937,11 +11937,11 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12345,11 +12345,11 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12413,11 +12413,11 @@
         <v>1</v>
       </c>
       <c r="G344" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12447,11 +12447,11 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12481,11 +12481,11 @@
         <v>1</v>
       </c>
       <c r="G346" t="n">
-        <v>0</v>
+        <v>9131</v>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12515,11 +12515,11 @@
         <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12549,11 +12549,11 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12583,11 +12583,11 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>1015</v>
+        <v>0</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13569,7 +13569,7 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14181,11 +14181,11 @@
         <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14215,11 +14215,11 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14249,11 +14249,11 @@
         <v>1</v>
       </c>
       <c r="G398" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14283,11 +14283,11 @@
         <v>1</v>
       </c>
       <c r="G399" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14351,11 +14351,11 @@
         <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>1616</v>
+        <v>0</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14832,6 +14832,618 @@
       <c r="H415" t="inlineStr">
         <is>
           <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C416" t="n">
+        <v>11300</v>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Practice 1</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F416" t="b">
+        <v>1</v>
+      </c>
+      <c r="G416" t="n">
+        <v>0</v>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>race_control</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C417" t="n">
+        <v>11300</v>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Practice 1</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F417" t="b">
+        <v>1</v>
+      </c>
+      <c r="G417" t="n">
+        <v>0</v>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>intervals</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C418" t="n">
+        <v>11300</v>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Practice 1</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F418" t="b">
+        <v>1</v>
+      </c>
+      <c r="G418" t="n">
+        <v>0</v>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C419" t="n">
+        <v>11300</v>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Practice 1</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F419" t="b">
+        <v>1</v>
+      </c>
+      <c r="G419" t="n">
+        <v>0</v>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>stints</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C420" t="n">
+        <v>11300</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Practice 1</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F420" t="b">
+        <v>1</v>
+      </c>
+      <c r="G420" t="n">
+        <v>0</v>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>pit</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C421" t="n">
+        <v>11300</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Practice 1</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F421" t="b">
+        <v>0</v>
+      </c>
+      <c r="G421" t="n">
+        <v>0</v>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>skipped_not_applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>starting_grid</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C422" t="n">
+        <v>11300</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Practice 1</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F422" t="b">
+        <v>1</v>
+      </c>
+      <c r="G422" t="n">
+        <v>0</v>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>drivers</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C423" t="n">
+        <v>11300</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Practice 1</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F423" t="b">
+        <v>1</v>
+      </c>
+      <c r="G423" t="n">
+        <v>18</v>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>team_radio</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C424" t="n">
+        <v>11300</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Practice 1</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F424" t="b">
+        <v>1</v>
+      </c>
+      <c r="G424" t="n">
+        <v>6</v>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C425" t="n">
+        <v>11301</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Practice 2</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F425" t="b">
+        <v>1</v>
+      </c>
+      <c r="G425" t="n">
+        <v>85</v>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>race_control</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C426" t="n">
+        <v>11301</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Practice 2</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F426" t="b">
+        <v>1</v>
+      </c>
+      <c r="G426" t="n">
+        <v>52</v>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>intervals</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C427" t="n">
+        <v>11301</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Practice 2</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F427" t="b">
+        <v>1</v>
+      </c>
+      <c r="G427" t="n">
+        <v>0</v>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C428" t="n">
+        <v>11301</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Practice 2</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F428" t="b">
+        <v>1</v>
+      </c>
+      <c r="G428" t="n">
+        <v>424</v>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>stints</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C429" t="n">
+        <v>11301</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Practice 2</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F429" t="b">
+        <v>1</v>
+      </c>
+      <c r="G429" t="n">
+        <v>118</v>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>pit</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C430" t="n">
+        <v>11301</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Practice 2</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F430" t="b">
+        <v>0</v>
+      </c>
+      <c r="G430" t="n">
+        <v>0</v>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>skipped_not_applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>starting_grid</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C431" t="n">
+        <v>11301</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Practice 2</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F431" t="b">
+        <v>1</v>
+      </c>
+      <c r="G431" t="n">
+        <v>0</v>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>drivers</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C432" t="n">
+        <v>11301</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Practice 2</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F432" t="b">
+        <v>1</v>
+      </c>
+      <c r="G432" t="n">
+        <v>22</v>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>team_radio</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C433" t="n">
+        <v>11301</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Practice 2</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F433" t="b">
+        <v>1</v>
+      </c>
+      <c r="G433" t="n">
+        <v>6</v>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14893,11 +15505,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4195</v>
+        <v>4081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>cc8c69791e6855efc7065a8872a4ab903a1325a7b33d85128f68f1e49b41e28f</t>
+          <t>56ba49a019af8554a4ecc9508eb94c2a70967f97dad7906426d41351d65eefb8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14923,11 +15535,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1239</v>
+        <v>1034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6cf53eb51aefd15d9c70465f499a8ba1770bba08b7b7442bddc17e3c5e21ede5</t>
+          <t>22fc80118750717f52c6d0c5136e34ffd06e491e76fde850a74a8c9e49b401fb</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -14953,11 +15565,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28324</v>
+        <v>58118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>343345dc92bc26079449276f72c6ec61d8423a11ff243facc4a624c3cde21b2d</t>
+          <t>5ebe1ac9d2a64b2d46fe20fd93ca442a4aa4ce474deb5ee6ff9fea8e8be4e688</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -14983,11 +15595,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10179</v>
+        <v>6912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5c7908201f48f0742d240a4a9d3c4496d6d82d0616177bb7bc9e3579e2728709</t>
+          <t>8ff2ca8a0da40c13644cd234eec36bfcf9ae2bbacf056edd9226e3dc68fff817</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15013,11 +15625,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2187</v>
+        <v>1861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>83cbcaddde403d9867ca7ca1f0d9ce8c83afe68239153f1befa4a34b5cdbfa78</t>
+          <t>4688ea9f6e59899460e2f2c6f5cce6f83ac37820c436f19606871283c45bd503</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15043,11 +15655,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>dfcba5f67065e5a2adb89367563b21ca355e83e070fbf98fab7c7a1eab6614ea</t>
+          <t>8b0da5d189330f0124d209989d7520843e46a6e0ae4b7d575d7f2d50a36234a7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15103,11 +15715,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>479</v>
+        <v>509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>e01f2ad8379d793e11bc0cb7fb483e3973e1d47ebe95ae05979c21e1af88899e</t>
+          <t>e3801b908a10ab9c68740de83593f544bdace8eca835adc5682a88f7f0fa19c2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15133,11 +15745,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>07548b2dfa24b8b8680138dd329c2b3f7dbb859084b6b8cf5350bd3192358175</t>
+          <t>e89a67b2469fdc6171f5f3a798e288252df3467570cf0bbe9f2885dc2f09d2cc</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15162,7 +15774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18375,6 +18987,142 @@
         <v>1</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>11300</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Practice 1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-06-12T11:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-06-12T12:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G48" t="n">
+        <v>15</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Catalunya</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O48" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>11301</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Practice 2</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-06-12T15:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-06-12T16:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G49" t="n">
+        <v>15</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Catalunya</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O49" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5895</v>
+        <v>6170</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3180</v>
+        <v>3716</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>202364</v>
+        <v>279138</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22964</v>
+        <v>19846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3524</v>
+        <v>2987</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>426</v>
+        <v>377</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>900</v>
+        <v>886</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2111,11 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1070</v>
+        <v>0</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3845,11 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4151,11 +4151,11 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5069,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5103,11 +5103,11 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5171,11 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>922</v>
+        <v>0</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5205,11 +5205,11 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5273,11 +5273,11 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5307,11 +5307,11 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5613,11 +5613,11 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6531,11 +6531,11 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6599,11 +6599,11 @@
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6633,11 +6633,11 @@
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6701,11 +6701,11 @@
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6735,11 +6735,11 @@
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6803,11 +6803,11 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9897,7 +9897,7 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11121,11 +11121,11 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11189,11 +11189,11 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11223,11 +11223,11 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11291,11 +11291,11 @@
         <v>1</v>
       </c>
       <c r="G311" t="n">
-        <v>981</v>
+        <v>0</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11325,11 +11325,11 @@
         <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11393,11 +11393,11 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>1035</v>
+        <v>0</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12311,11 +12311,11 @@
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12345,11 +12345,11 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13093,11 +13093,11 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0</v>
+        <v>22532</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13127,11 +13127,11 @@
         <v>1</v>
       </c>
       <c r="G365" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13161,11 +13161,11 @@
         <v>1</v>
       </c>
       <c r="G366" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13195,11 +13195,11 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13569,11 +13569,11 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13637,11 +13637,11 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13671,11 +13671,11 @@
         <v>1</v>
       </c>
       <c r="G381" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>816</v>
+        <v>0</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14181,11 +14181,11 @@
         <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14215,11 +14215,11 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14249,11 +14249,11 @@
         <v>1</v>
       </c>
       <c r="G398" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14283,11 +14283,11 @@
         <v>1</v>
       </c>
       <c r="G399" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14487,11 +14487,11 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14521,11 +14521,11 @@
         <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14555,11 +14555,11 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14589,11 +14589,11 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14623,11 +14623,11 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>29916</v>
+        <v>0</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14793,11 +14793,11 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14827,11 +14827,11 @@
         <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14861,11 +14861,11 @@
         <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14895,11 +14895,11 @@
         <v>1</v>
       </c>
       <c r="G417" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14963,11 +14963,11 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14997,11 +14997,11 @@
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15269,11 +15269,11 @@
         <v>1</v>
       </c>
       <c r="G428" t="n">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15303,11 +15303,11 @@
         <v>1</v>
       </c>
       <c r="G429" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15405,11 +15405,11 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15439,11 +15439,11 @@
         <v>1</v>
       </c>
       <c r="G433" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15473,11 +15473,11 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15507,11 +15507,11 @@
         <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15575,11 +15575,11 @@
         <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15711,7 +15711,7 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16323,11 +16323,11 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16357,11 +16357,11 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16629,11 +16629,11 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16663,11 +16663,11 @@
         <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16697,11 +16697,11 @@
         <v>1</v>
       </c>
       <c r="G470" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16731,11 +16731,11 @@
         <v>1</v>
       </c>
       <c r="G471" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16799,11 +16799,11 @@
         <v>1</v>
       </c>
       <c r="G473" t="n">
-        <v>0</v>
+        <v>509</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16833,11 +16833,11 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16935,7 +16935,7 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17139,11 +17139,11 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17241,11 +17241,11 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17547,11 +17547,11 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17581,11 +17581,11 @@
         <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17615,11 +17615,11 @@
         <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17649,11 +17649,11 @@
         <v>1</v>
       </c>
       <c r="G498" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17683,11 +17683,11 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>0</v>
+        <v>26312</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18023,11 +18023,11 @@
         <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18057,11 +18057,11 @@
         <v>1</v>
       </c>
       <c r="G510" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18159,7 +18159,7 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
@@ -18635,11 +18635,11 @@
         <v>1</v>
       </c>
       <c r="G527" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18669,11 +18669,11 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18703,11 +18703,11 @@
         <v>1</v>
       </c>
       <c r="G529" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
@@ -19111,11 +19111,11 @@
         <v>1</v>
       </c>
       <c r="G541" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19145,11 +19145,11 @@
         <v>1</v>
       </c>
       <c r="G542" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19179,11 +19179,11 @@
         <v>1</v>
       </c>
       <c r="G543" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>0</v>
+        <v>28253</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19689,11 +19689,11 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19757,11 +19757,11 @@
         <v>1</v>
       </c>
       <c r="G560" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19791,11 +19791,11 @@
         <v>1</v>
       </c>
       <c r="G561" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19859,11 +19859,11 @@
         <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19995,11 +19995,11 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20029,11 +20029,11 @@
         <v>1</v>
       </c>
       <c r="G568" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20063,11 +20063,11 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20097,11 +20097,11 @@
         <v>1</v>
       </c>
       <c r="G570" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20165,11 +20165,11 @@
         <v>1</v>
       </c>
       <c r="G572" t="n">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20199,11 +20199,11 @@
         <v>1</v>
       </c>
       <c r="G573" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20301,11 +20301,11 @@
         <v>1</v>
       </c>
       <c r="G576" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20369,11 +20369,11 @@
         <v>1</v>
       </c>
       <c r="G578" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21083,11 +21083,11 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>734</v>
+        <v>0</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21117,11 +21117,11 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21219,11 +21219,11 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21253,11 +21253,11 @@
         <v>1</v>
       </c>
       <c r="G604" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21287,11 +21287,11 @@
         <v>1</v>
       </c>
       <c r="G605" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21321,11 +21321,11 @@
         <v>1</v>
       </c>
       <c r="G606" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21525,7 +21525,7 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21695,11 +21695,11 @@
         <v>1</v>
       </c>
       <c r="G617" t="n">
-        <v>0</v>
+        <v>513</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21729,11 +21729,11 @@
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21831,11 +21831,11 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         <v>1</v>
       </c>
       <c r="G622" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21899,11 +21899,11 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21933,11 +21933,11 @@
         <v>1</v>
       </c>
       <c r="G624" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22001,11 +22001,11 @@
         <v>1</v>
       </c>
       <c r="G626" t="n">
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22137,7 +22137,7 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
@@ -22171,11 +22171,11 @@
         <v>1</v>
       </c>
       <c r="G631" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22205,11 +22205,11 @@
         <v>1</v>
       </c>
       <c r="G632" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22239,11 +22239,11 @@
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22273,11 +22273,11 @@
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>0</v>
+        <v>29593</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22307,11 +22307,11 @@
         <v>1</v>
       </c>
       <c r="G635" t="n">
-        <v>0</v>
+        <v>536</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22341,11 +22341,11 @@
         <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22543,11 +22543,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5895</v>
+        <v>6170</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>a67fa0df17cfd183ef791973776957fdb063a69a26d16e9c1c5a2d7fdb996399</t>
+          <t>1846e2e91573e44f910455a456f61dcac51d04940588647eb18698a4ffa9ba8a</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -22573,11 +22573,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3180</v>
+        <v>3716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33f33770bb835a8ba8c071962d680f6e238141cf633f2b63fa43016e03d5435f</t>
+          <t>c1fd6a9962a1c5a1498928e9b5f966d30b4a4122408f4de052c6bcfcc2802b2a</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -22603,11 +22603,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>202364</v>
+        <v>279138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1beac40b745d58ecc39146123b435f15fb70ba864f510c154cd2f238008a0bf7</t>
+          <t>68b2ef35a52095112f474be6bc396eadfa2adc7eec037748fcbe7e25d74c2c4f</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -22633,11 +22633,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22964</v>
+        <v>19846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8d7bcda0ef3cde92879cec5dc81b45ec80069a7241fc7108e0eacb53d0eafac8</t>
+          <t>0ffa35110bf3349e81e7fac4bfb93383736eae0bf0db923911769c256ba47d08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -22663,11 +22663,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3524</v>
+        <v>2987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31a5b9d3acab93d913fd4b792c1b2a7c02d958e7b13c1e979b1ac1a531b4aef0</t>
+          <t>e11f3d5d542d4c8572dcc0acc5aa89e4c1cc196942d512486fa85a871776cf66</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -22693,11 +22693,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>426</v>
+        <v>377</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5e69d78d1ea098c525aeaebb78974b9dbfe1d6167486beababeaeb1f60239f4b</t>
+          <t>e658df0ae613951ab7bda5445c25ebc2ad70b0fa1a2fa80e5e7ebfdf90795d8f</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -22723,11 +22723,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>c1293537b8179798a1b04d3369372ff36d40b1ea7925480c53856760809710d1</t>
+          <t>ed2943816c3a332350339f4de639deded081716f9f57b3ebd3a835ade661df73</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -22753,11 +22753,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>900</v>
+        <v>886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>a32f0f3c56e5ace6816d6ac60162869fad408bfeace86be6eed0de3c933fa7cf</t>
+          <t>6a379ca01925d4d95c644e0496e4251e37803bc317f18bf27982698cf695b394</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -22783,11 +22783,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>193242256db611d6fe7bf26bf6090960e3de352c1805b59e30c90d09291ebb0f</t>
+          <t>c8ec779551a244a41656480a70489fb01f06778d3c00c65c5943a706ae74cc1d</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5580</v>
+        <v>6579</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3079</v>
+        <v>3639</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>169517</v>
+        <v>279071</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22264</v>
+        <v>26706</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3475</v>
+        <v>3672</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>862</v>
+        <v>1065</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>227</v>
+        <v>383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3029,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3063,11 +3063,11 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1070</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>1041</v>
+        <v>0</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>9019</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5069,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5103,11 +5103,11 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5171,11 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5205,11 +5205,11 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5273,11 +5273,11 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5307,11 +5307,11 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5375,11 +5375,11 @@
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5409,11 +5409,11 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5443,11 +5443,11 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>20663</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5477,11 +5477,11 @@
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5511,11 +5511,11 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5545,11 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6089,11 +6089,11 @@
         <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6123,11 +6123,11 @@
         <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6225,11 +6225,11 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7449,11 +7449,11 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8673,7 +8673,7 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9285,11 +9285,11 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9897,7 +9897,7 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10815,11 +10815,11 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>9347</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11019,11 +11019,11 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11121,11 +11121,11 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11189,11 +11189,11 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11223,11 +11223,11 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>0</v>
+        <v>25483</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11733,7 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -11937,11 +11937,11 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>1035</v>
+        <v>0</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12311,11 +12311,11 @@
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12345,7 +12345,7 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
@@ -12413,11 +12413,11 @@
         <v>1</v>
       </c>
       <c r="G344" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12447,11 +12447,11 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12481,11 +12481,11 @@
         <v>1</v>
       </c>
       <c r="G346" t="n">
-        <v>0</v>
+        <v>9131</v>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12515,11 +12515,11 @@
         <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12549,11 +12549,11 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12583,11 +12583,11 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12651,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12753,11 +12753,11 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12821,11 +12821,11 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>0</v>
+        <v>1449</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12957,11 +12957,11 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12991,11 +12991,11 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13025,11 +13025,11 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13059,11 +13059,11 @@
         <v>1</v>
       </c>
       <c r="G363" t="n">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13093,11 +13093,11 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0</v>
+        <v>22532</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13127,11 +13127,11 @@
         <v>1</v>
       </c>
       <c r="G365" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13161,11 +13161,11 @@
         <v>1</v>
       </c>
       <c r="G366" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13195,11 +13195,11 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>1015</v>
+        <v>0</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13569,11 +13569,11 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13637,11 +13637,11 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13671,11 +13671,11 @@
         <v>1</v>
       </c>
       <c r="G381" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14351,11 +14351,11 @@
         <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>1616</v>
+        <v>0</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14385,11 +14385,11 @@
         <v>1</v>
       </c>
       <c r="G402" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14453,11 +14453,11 @@
         <v>1</v>
       </c>
       <c r="G404" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14487,11 +14487,11 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14521,11 +14521,11 @@
         <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14555,11 +14555,11 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14589,11 +14589,11 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14623,11 +14623,11 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>29916</v>
+        <v>0</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
@@ -14963,11 +14963,11 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14997,11 +14997,11 @@
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15099,11 +15099,11 @@
         <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15133,11 +15133,11 @@
         <v>1</v>
       </c>
       <c r="G424" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15167,11 +15167,11 @@
         <v>1</v>
       </c>
       <c r="G425" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15201,11 +15201,11 @@
         <v>1</v>
       </c>
       <c r="G426" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15269,11 +15269,11 @@
         <v>1</v>
       </c>
       <c r="G428" t="n">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15575,11 +15575,11 @@
         <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15711,7 +15711,7 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
@@ -16323,11 +16323,11 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16357,11 +16357,11 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16425,11 +16425,11 @@
         <v>1</v>
       </c>
       <c r="G462" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16493,11 +16493,11 @@
         <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16527,11 +16527,11 @@
         <v>1</v>
       </c>
       <c r="G465" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16629,11 +16629,11 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16663,11 +16663,11 @@
         <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16799,11 +16799,11 @@
         <v>1</v>
       </c>
       <c r="G473" t="n">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16833,11 +16833,11 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16935,7 +16935,7 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>982</v>
+        <v>0</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,7 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
@@ -17921,11 +17921,11 @@
         <v>1</v>
       </c>
       <c r="G506" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17955,11 +17955,11 @@
         <v>1</v>
       </c>
       <c r="G507" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18023,11 +18023,11 @@
         <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>0</v>
+        <v>788</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18057,11 +18057,11 @@
         <v>1</v>
       </c>
       <c r="G510" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18261,11 +18261,11 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18329,11 +18329,11 @@
         <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>0</v>
+        <v>839</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18363,11 +18363,11 @@
         <v>1</v>
       </c>
       <c r="G519" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18465,11 +18465,11 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18499,11 +18499,11 @@
         <v>1</v>
       </c>
       <c r="G523" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18533,11 +18533,11 @@
         <v>1</v>
       </c>
       <c r="G524" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18567,11 +18567,11 @@
         <v>1</v>
       </c>
       <c r="G525" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>9414</v>
+        <v>0</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18635,11 +18635,11 @@
         <v>1</v>
       </c>
       <c r="G527" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18669,11 +18669,11 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19689,11 +19689,11 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19791,11 +19791,11 @@
         <v>1</v>
       </c>
       <c r="G561" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19859,11 +19859,11 @@
         <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19995,11 +19995,11 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20029,11 +20029,11 @@
         <v>1</v>
       </c>
       <c r="G568" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20063,11 +20063,11 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20097,11 +20097,11 @@
         <v>1</v>
       </c>
       <c r="G570" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20165,11 +20165,11 @@
         <v>1</v>
       </c>
       <c r="G572" t="n">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>0</v>
+        <v>23116</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20913,11 +20913,11 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20947,11 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20981,11 +20981,11 @@
         <v>1</v>
       </c>
       <c r="G596" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21015,11 +21015,11 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21083,11 +21083,11 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>0</v>
+        <v>734</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21117,11 +21117,11 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21219,11 +21219,11 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21253,11 +21253,11 @@
         <v>1</v>
       </c>
       <c r="G604" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21287,11 +21287,11 @@
         <v>1</v>
       </c>
       <c r="G605" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21695,11 +21695,11 @@
         <v>1</v>
       </c>
       <c r="G617" t="n">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         <v>1</v>
       </c>
       <c r="G622" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21899,11 +21899,11 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21933,11 +21933,11 @@
         <v>1</v>
       </c>
       <c r="G624" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22001,11 +22001,11 @@
         <v>1</v>
       </c>
       <c r="G626" t="n">
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22137,11 +22137,11 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22171,11 +22171,11 @@
         <v>1</v>
       </c>
       <c r="G631" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22205,11 +22205,11 @@
         <v>1</v>
       </c>
       <c r="G632" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22239,11 +22239,11 @@
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22273,11 +22273,11 @@
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>0</v>
+        <v>29593</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22307,11 +22307,11 @@
         <v>1</v>
       </c>
       <c r="G635" t="n">
-        <v>0</v>
+        <v>536</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22341,11 +22341,11 @@
         <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22375,11 +22375,11 @@
         <v>1</v>
       </c>
       <c r="G637" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22443,11 +22443,11 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22477,11 +22477,11 @@
         <v>1</v>
       </c>
       <c r="G640" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22543,11 +22543,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5580</v>
+        <v>6579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32dccd8caf21de9adc31590aa5125199b69584feb8a8711490a21fc29d1eb707</t>
+          <t>3e0a9bf555583f6f38f427a255eaa4143de407f66b85c0afb1fdb87548bfd574</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -22573,11 +22573,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3079</v>
+        <v>3639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>e6700e85a3ba2da80e3debd70601bce337b468346b08eca8a8cbc399c95d22c8</t>
+          <t>8052ab506adcc85836c77a64f2a3101c920ebda01ea12abdb0f65723690b8e3b</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -22603,11 +22603,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>169517</v>
+        <v>279071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>c1aedecca35300c437d1b642aa350713d0f44972fc75674a647a166982cb68c8</t>
+          <t>53c2fe51365b6a428e9987a96ad1a2533b398981541a707215f0fa1907b160f7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -22633,11 +22633,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22264</v>
+        <v>26706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>a26557dec9f8bd7cb5f568beba83b29a066f7e78e94873e24b92ff9ba82b1f6e</t>
+          <t>fb160072f6dab960f9982ba3afb60b1e2cff07412f00408577949474c1d99243</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -22663,11 +22663,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3475</v>
+        <v>3672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>379fb67402edc6fd067a7694227f97564f971e7a2b1dc12631f57395687dc248</t>
+          <t>41192b252b6edf576ff95f3e355b5ca2f9ba949a71845672f8f3707c43b51237</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -22693,11 +22693,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cba3251b27c0d1af8b6625be8c16be12103566320afe55fe0480cd8cb082c35e</t>
+          <t>c7b0b7868769daaeb543341624e00fde61f15013da1396d8b1a013913e09d6d9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -22723,11 +22723,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>574f75f989863c7cc1d0f90e1a035036602d73d551e67a13a48362294a9114f3</t>
+          <t>bd7ec52aa1e3ded9f655c31e6f01b05f97abd6a5dd82429641691c32b09e906b</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -22753,11 +22753,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>862</v>
+        <v>1065</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>f9cf369ecdc535fd66a0d625f5c217eb236c7b8070a7a33703acb7d18a849d29</t>
+          <t>60e5c9ee06640d46983071dc99abe86df829f4d59d564c66b914579cff66b704</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -22783,11 +22783,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>383</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6a56f9c0451dd8b3a3ad996e879ef7b03919916471cb0df44bfb0bff816ff4f0</t>
+          <t>92463be827dccfebc35e06677d92c0231b288cfa2affd9a37b6cf090d98e6e7c</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5515</v>
+        <v>6345</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2766</v>
+        <v>3370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>136766</v>
+        <v>251897</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21251</v>
+        <v>20829</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2681</v>
+        <v>3482</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>301</v>
+        <v>274</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>258</v>
+        <v>214</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2111,11 +2111,11 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2145,11 +2145,11 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3165,11 +3165,11 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3233,11 +3233,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3267,11 +3267,11 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3335,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1070</v>
+        <v>0</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3981,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4015,11 +4015,11 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4083,11 +4083,11 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4151,11 +4151,11 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4389,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>1041</v>
+        <v>0</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4695,11 +4695,11 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>9019</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5307,11 +5307,11 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5375,11 +5375,11 @@
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5409,11 +5409,11 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5443,11 +5443,11 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>20663</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5477,11 +5477,11 @@
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5511,11 +5511,11 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5545,11 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5987,11 +5987,11 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6021,11 +6021,11 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7041,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7449,11 +7449,11 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8673,7 +8673,7 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -9285,11 +9285,11 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10271,11 +10271,11 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10373,11 +10373,11 @@
         <v>1</v>
       </c>
       <c r="G284" t="n">
-        <v>0</v>
+        <v>670</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>941</v>
+        <v>0</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11121,11 +11121,11 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11189,11 +11189,11 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11223,11 +11223,11 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11291,11 +11291,11 @@
         <v>1</v>
       </c>
       <c r="G311" t="n">
-        <v>981</v>
+        <v>0</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11325,11 +11325,11 @@
         <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>0</v>
+        <v>25483</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11733,7 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>1035</v>
+        <v>0</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12753,11 +12753,11 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12821,11 +12821,11 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>1449</v>
+        <v>0</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13161,11 +13161,11 @@
         <v>1</v>
       </c>
       <c r="G366" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13195,11 +13195,11 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>1015</v>
+        <v>0</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13569,11 +13569,11 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14181,7 +14181,7 @@
         <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
@@ -14487,11 +14487,11 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14521,11 +14521,11 @@
         <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14555,11 +14555,11 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14589,11 +14589,11 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14623,11 +14623,11 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>0</v>
+        <v>29916</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14793,11 +14793,11 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14827,11 +14827,11 @@
         <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14861,11 +14861,11 @@
         <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14895,11 +14895,11 @@
         <v>1</v>
       </c>
       <c r="G417" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14963,11 +14963,11 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14997,11 +14997,11 @@
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15099,11 +15099,11 @@
         <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15133,11 +15133,11 @@
         <v>1</v>
       </c>
       <c r="G424" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15167,11 +15167,11 @@
         <v>1</v>
       </c>
       <c r="G425" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15201,11 +15201,11 @@
         <v>1</v>
       </c>
       <c r="G426" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15711,11 +15711,11 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15745,11 +15745,11 @@
         <v>1</v>
       </c>
       <c r="G442" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15779,11 +15779,11 @@
         <v>1</v>
       </c>
       <c r="G443" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15813,11 +15813,11 @@
         <v>1</v>
       </c>
       <c r="G444" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15881,11 +15881,11 @@
         <v>1</v>
       </c>
       <c r="G446" t="n">
-        <v>0</v>
+        <v>1116</v>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15915,11 +15915,11 @@
         <v>1</v>
       </c>
       <c r="G447" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15983,11 +15983,11 @@
         <v>1</v>
       </c>
       <c r="G449" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
@@ -16357,11 +16357,11 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16935,11 +16935,11 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17241,11 +17241,11 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,7 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
@@ -17581,11 +17581,11 @@
         <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17615,11 +17615,11 @@
         <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17649,11 +17649,11 @@
         <v>1</v>
       </c>
       <c r="G498" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17683,11 +17683,11 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>0</v>
+        <v>26312</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17717,11 +17717,11 @@
         <v>1</v>
       </c>
       <c r="G500" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17751,11 +17751,11 @@
         <v>1</v>
       </c>
       <c r="G501" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17785,11 +17785,11 @@
         <v>1</v>
       </c>
       <c r="G502" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17853,11 +17853,11 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18261,11 +18261,11 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18771,7 +18771,7 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
@@ -18805,11 +18805,11 @@
         <v>1</v>
       </c>
       <c r="G532" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18839,11 +18839,11 @@
         <v>1</v>
       </c>
       <c r="G533" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18873,11 +18873,11 @@
         <v>1</v>
       </c>
       <c r="G534" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18941,11 +18941,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="n">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18975,11 +18975,11 @@
         <v>1</v>
       </c>
       <c r="G537" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19077,11 +19077,11 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19111,11 +19111,11 @@
         <v>1</v>
       </c>
       <c r="G541" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19145,11 +19145,11 @@
         <v>1</v>
       </c>
       <c r="G542" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19179,11 +19179,11 @@
         <v>1</v>
       </c>
       <c r="G543" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>0</v>
+        <v>28253</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19689,11 +19689,11 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19757,11 +19757,11 @@
         <v>1</v>
       </c>
       <c r="G560" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19791,11 +19791,11 @@
         <v>1</v>
       </c>
       <c r="G561" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19859,11 +19859,11 @@
         <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19995,11 +19995,11 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20607,11 +20607,11 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20641,11 +20641,11 @@
         <v>1</v>
       </c>
       <c r="G586" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>0</v>
+        <v>23116</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20947,11 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20981,11 +20981,11 @@
         <v>1</v>
       </c>
       <c r="G596" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21015,11 +21015,11 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21831,11 +21831,11 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         <v>1</v>
       </c>
       <c r="G622" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21899,11 +21899,11 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21933,11 +21933,11 @@
         <v>1</v>
       </c>
       <c r="G624" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22001,11 +22001,11 @@
         <v>1</v>
       </c>
       <c r="G626" t="n">
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22137,11 +22137,11 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22171,11 +22171,11 @@
         <v>1</v>
       </c>
       <c r="G631" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22205,11 +22205,11 @@
         <v>1</v>
       </c>
       <c r="G632" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22239,11 +22239,11 @@
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22273,11 +22273,11 @@
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>29593</v>
+        <v>0</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22307,11 +22307,11 @@
         <v>1</v>
       </c>
       <c r="G635" t="n">
-        <v>536</v>
+        <v>0</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22341,11 +22341,11 @@
         <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22375,11 +22375,11 @@
         <v>1</v>
       </c>
       <c r="G637" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22477,11 +22477,11 @@
         <v>1</v>
       </c>
       <c r="G640" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22543,11 +22543,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5515</v>
+        <v>6345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>bb8af4748ed9b0a2e30a22f97a682a9db739466dc6c014dec08e846bec6c34fe</t>
+          <t>1a5ff0b1313b7bea1f316b035466041787c7046ca544439c4333bc7144869d03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -22573,11 +22573,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2766</v>
+        <v>3370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2b70d6b7baf8da025d175424828e7af658033483fddabf2c0c750bf3e3da5f7e</t>
+          <t>6a73d0d6756bd03086b803911fb0b20e1b8da1cbf5eea16cf233c31c7fad6a70</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -22603,11 +22603,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>136766</v>
+        <v>251897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8f35d00cfa8d1e0901f051df94610a8c5e391772c06c84a59035f0881aabf7fa</t>
+          <t>e696c1fb16dfb23d30f47c798abb31b64fb6c567ad4c4476adf164d6bde60f6a</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -22633,11 +22633,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21251</v>
+        <v>20829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>d57a9bee42c26867d78ec09c606d19f381253d76ec4623addb5ff1c7548afc3a</t>
+          <t>668cef2fbd9c25d74c5b1a5b3149d0d90f5c809534e6f2da73ce34b1615db4dc</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -22663,11 +22663,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2681</v>
+        <v>3482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7cb123d119d90bd2d8d51a2170598f8e3706ee16bcfca91bdc3de64828968d01</t>
+          <t>6e424ceb962c6452f6bee8c0b5ab67391e888bdfeb8a67afa2658d4794fd42b7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -22693,11 +22693,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>301</v>
+        <v>274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>d68a752f24c9c275f742e808ac6918a5f9cdf9caf1d0b8b38ae40616568c55ae</t>
+          <t>f85a9f4d64e7af400b16edc97a2a254da9af2f0504d98120248225062c3f601f</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -22723,11 +22723,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17981e6131537bba939348e3caf537c90697187f4d77e41eeaa16d3c53bc5160</t>
+          <t>b923f948e417782875f7b498eecfc8e7d902e12815e5422c566eafea3a5e4dd1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>05274593cd2fd905cedb050d8fb9d53a42969545966fb2f7b8b6fae639e19822</t>
+          <t>427df0ee1b365fd9d93d7cd8770930c0118697b7f8864bf04f495a57b7f02eae</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -22783,11 +22783,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>258</v>
+        <v>214</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>682f2f43f2a80132659dd945e541886238dd2ecb22f473d0c7b3ec6fa761ec1b</t>
+          <t>2456655b3dd56e2f36b3c92ada9935a091cb3aa3bd1d6a9501e62cfd8e5323d7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4204</v>
+        <v>6173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2142</v>
+        <v>3655</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>87706</v>
+        <v>243032</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13851</v>
+        <v>20915</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2526</v>
+        <v>3419</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>187</v>
+        <v>450</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>642</v>
+        <v>891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>197</v>
+        <v>393</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2587,11 +2587,11 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1070</v>
+        <v>0</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4083,11 +4083,11 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4151,11 +4151,11 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4695,11 +4695,11 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>9019</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5069,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5307,11 +5307,11 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5375,11 +5375,11 @@
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5409,11 +5409,11 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5443,11 +5443,11 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>20663</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5477,11 +5477,11 @@
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5511,11 +5511,11 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5545,11 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9285,7 +9285,7 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10373,11 +10373,11 @@
         <v>1</v>
       </c>
       <c r="G284" t="n">
-        <v>670</v>
+        <v>0</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12345,7 +12345,7 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
@@ -12651,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13569,11 +13569,11 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13637,11 +13637,11 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13671,11 +13671,11 @@
         <v>1</v>
       </c>
       <c r="G381" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14487,11 +14487,11 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14521,11 +14521,11 @@
         <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14555,11 +14555,11 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14589,11 +14589,11 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14623,11 +14623,11 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>0</v>
+        <v>29916</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14793,11 +14793,11 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14827,11 +14827,11 @@
         <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15099,11 +15099,11 @@
         <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15133,11 +15133,11 @@
         <v>1</v>
       </c>
       <c r="G424" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15167,11 +15167,11 @@
         <v>1</v>
       </c>
       <c r="G425" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15201,11 +15201,11 @@
         <v>1</v>
       </c>
       <c r="G426" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15269,11 +15269,11 @@
         <v>1</v>
       </c>
       <c r="G428" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15303,11 +15303,11 @@
         <v>1</v>
       </c>
       <c r="G429" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15405,11 +15405,11 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15439,11 +15439,11 @@
         <v>1</v>
       </c>
       <c r="G433" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15473,11 +15473,11 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15507,11 +15507,11 @@
         <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15575,11 +15575,11 @@
         <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15711,11 +15711,11 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15745,11 +15745,11 @@
         <v>1</v>
       </c>
       <c r="G442" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15779,11 +15779,11 @@
         <v>1</v>
       </c>
       <c r="G443" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15813,11 +15813,11 @@
         <v>1</v>
       </c>
       <c r="G444" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15881,11 +15881,11 @@
         <v>1</v>
       </c>
       <c r="G446" t="n">
-        <v>0</v>
+        <v>1116</v>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15915,11 +15915,11 @@
         <v>1</v>
       </c>
       <c r="G447" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15983,11 +15983,11 @@
         <v>1</v>
       </c>
       <c r="G449" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>0</v>
+        <v>25022</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16323,11 +16323,11 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16357,11 +16357,11 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16425,11 +16425,11 @@
         <v>1</v>
       </c>
       <c r="G462" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16493,11 +16493,11 @@
         <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16527,11 +16527,11 @@
         <v>1</v>
       </c>
       <c r="G465" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
@@ -16731,11 +16731,11 @@
         <v>1</v>
       </c>
       <c r="G471" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17547,11 +17547,11 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17581,11 +17581,11 @@
         <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17615,11 +17615,11 @@
         <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17649,11 +17649,11 @@
         <v>1</v>
       </c>
       <c r="G498" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17683,11 +17683,11 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>0</v>
+        <v>26312</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17717,11 +17717,11 @@
         <v>1</v>
       </c>
       <c r="G500" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17751,11 +17751,11 @@
         <v>1</v>
       </c>
       <c r="G501" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17785,11 +17785,11 @@
         <v>1</v>
       </c>
       <c r="G502" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18023,11 +18023,11 @@
         <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>0</v>
+        <v>788</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18057,11 +18057,11 @@
         <v>1</v>
       </c>
       <c r="G510" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18805,11 +18805,11 @@
         <v>1</v>
       </c>
       <c r="G532" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18839,11 +18839,11 @@
         <v>1</v>
       </c>
       <c r="G533" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18873,11 +18873,11 @@
         <v>1</v>
       </c>
       <c r="G534" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18941,11 +18941,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="n">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18975,11 +18975,11 @@
         <v>1</v>
       </c>
       <c r="G537" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>0</v>
+        <v>28253</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19689,11 +19689,11 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20301,7 +20301,7 @@
         <v>1</v>
       </c>
       <c r="G576" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20607,11 +20607,11 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20641,11 +20641,11 @@
         <v>1</v>
       </c>
       <c r="G586" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>0</v>
+        <v>23116</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20913,11 +20913,11 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20947,11 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20981,11 +20981,11 @@
         <v>1</v>
       </c>
       <c r="G596" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21015,11 +21015,11 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22511,11 +22511,11 @@
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23055,11 +23055,11 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23089,11 +23089,11 @@
         <v>1</v>
       </c>
       <c r="G658" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23191,11 +23191,11 @@
         <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>0</v>
+        <v>11063</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23225,11 +23225,11 @@
         <v>1</v>
       </c>
       <c r="G662" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23259,11 +23259,11 @@
         <v>1</v>
       </c>
       <c r="G663" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23293,11 +23293,11 @@
         <v>1</v>
       </c>
       <c r="G664" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23361,7 +23361,7 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
@@ -23973,11 +23973,11 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24007,11 +24007,11 @@
         <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24073,11 +24073,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4204</v>
+        <v>6173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>cbcad4624c3c34e3dc20e842e544f642c1ad3db4b056590c3ad580ce81990cb3</t>
+          <t>947c703a1aa0367d70b774867d4d21abd3f3a8eeb236b6850825788d05bb4c5c</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -24103,11 +24103,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2142</v>
+        <v>3655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>d4795351caa603f9d7f87008e7f5bffc3008e3a16f39c872841be5b7e0ed03d4</t>
+          <t>142f01bf5b7d05a03fadcec11fe3d68e702225aeb7500c07e1bbd13f9af11624</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -24133,11 +24133,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>87706</v>
+        <v>243032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13c731c8a479a0890121fcdd962d6bc601ac4a9c2a6122f42fc63e1640a57c45</t>
+          <t>d476d4fe97bc38e09cfb90864491af0a498616e380d3d1a4ba21cc59af79a300</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -24163,11 +24163,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13851</v>
+        <v>20915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>e65a9e2ad04819a5885809150afb38d95292b6d08d53bc452db4ed0be139e9ae</t>
+          <t>b25def036e52f724e0d0546899b879899211f55a7b272fb152d74567f4480174</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -24193,11 +24193,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2526</v>
+        <v>3419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>93d8d2c54b2da49d9dcb413981054621f7dd5991e6d0b7ddafc2dfa26ec40f35</t>
+          <t>b5cbccb1f9b9f22d680f4e00caefc3fd7642b3f278b6644830a2dc2fc8734a3b</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -24223,11 +24223,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>187</v>
+        <v>450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>e50045c0d53551286692810dfbcfa126ed51ec89eee3c559f2e1afd468cb979f</t>
+          <t>2a87ad6d7938ebb145c96fcdb924a55888b506b9846d8c1b6ebf555021e74ab2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -24253,11 +24253,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1f7750fa81b7ee6b2d8a65bf1064b50a64c0722e8a14be497df69263e4788922</t>
+          <t>bb83681a45cb5db8ac79e5a1672f1846aa0cbbb5f33aa0eae3975a45b864d351</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -24283,11 +24283,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>642</v>
+        <v>891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>c42019f8f1ac5c8b7ce9d7b2238c0e3f3b096130650a0aec75bc805063173395</t>
+          <t>82d22ea4c6ee57a411b08e5232dc1714a8563e5973f72d7649f2a96cfb49e496</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -24313,11 +24313,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>197</v>
+        <v>393</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1338cd69055c99848980a3ff26f302c539a73900d0e20a484e7b5260c1f09518</t>
+          <t>75e3734c261a5cccf7ac5441d2a69b20ec3dfd35c9a520433c45bcc88a8e0503</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4779</v>
+        <v>6831</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2738</v>
+        <v>3965</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>185696</v>
+        <v>250495</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19143</v>
+        <v>27439</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3171</v>
+        <v>4150</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>391</v>
+        <v>502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>858</v>
+        <v>1036</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>279</v>
+        <v>361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2111,11 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2145,11 +2145,11 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3947,11 +3947,11 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3981,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4015,11 +4015,11 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4083,11 +4083,11 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>9019</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5987,11 +5987,11 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6021,11 +6021,11 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6531,11 +6531,11 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6599,11 +6599,11 @@
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6633,11 +6633,11 @@
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6701,11 +6701,11 @@
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6735,11 +6735,11 @@
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6803,11 +6803,11 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6837,11 +6837,11 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6905,11 +6905,11 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6939,11 +6939,11 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6973,11 +6973,11 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>28324</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7041,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8673,11 +8673,11 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9285,11 +9285,11 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10271,11 +10271,11 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>941</v>
+        <v>0</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10815,11 +10815,11 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>9347</v>
+        <v>0</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11019,11 +11019,11 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11053,11 +11053,11 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11121,11 +11121,11 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11189,11 +11189,11 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>0</v>
+        <v>25483</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11903,11 +11903,11 @@
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>0</v>
+        <v>843</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11937,11 +11937,11 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12515,11 +12515,11 @@
         <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12549,11 +12549,11 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12583,11 +12583,11 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12651,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12753,11 +12753,11 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13637,11 +13637,11 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13671,11 +13671,11 @@
         <v>1</v>
       </c>
       <c r="G381" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14521,11 +14521,11 @@
         <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14555,11 +14555,11 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14589,11 +14589,11 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15575,11 +15575,11 @@
         <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15711,11 +15711,11 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>0</v>
+        <v>25022</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16323,11 +16323,11 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16357,11 +16357,11 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16425,11 +16425,11 @@
         <v>1</v>
       </c>
       <c r="G462" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16493,11 +16493,11 @@
         <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16527,11 +16527,11 @@
         <v>1</v>
       </c>
       <c r="G465" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
@@ -16663,11 +16663,11 @@
         <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16697,11 +16697,11 @@
         <v>1</v>
       </c>
       <c r="G470" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16731,11 +16731,11 @@
         <v>1</v>
       </c>
       <c r="G471" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16799,11 +16799,11 @@
         <v>1</v>
       </c>
       <c r="G473" t="n">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16833,11 +16833,11 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16935,11 +16935,11 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17241,11 +17241,11 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17547,11 +17547,11 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17581,11 +17581,11 @@
         <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17615,11 +17615,11 @@
         <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17649,11 +17649,11 @@
         <v>1</v>
       </c>
       <c r="G498" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17853,11 +17853,11 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17887,11 +17887,11 @@
         <v>1</v>
       </c>
       <c r="G505" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17921,11 +17921,11 @@
         <v>1</v>
       </c>
       <c r="G506" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17955,11 +17955,11 @@
         <v>1</v>
       </c>
       <c r="G507" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18023,11 +18023,11 @@
         <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18057,11 +18057,11 @@
         <v>1</v>
       </c>
       <c r="G510" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18159,7 +18159,7 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
@@ -18431,11 +18431,11 @@
         <v>1</v>
       </c>
       <c r="G521" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18465,11 +18465,11 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18499,11 +18499,11 @@
         <v>1</v>
       </c>
       <c r="G523" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18533,11 +18533,11 @@
         <v>1</v>
       </c>
       <c r="G524" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18567,11 +18567,11 @@
         <v>1</v>
       </c>
       <c r="G525" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>0</v>
+        <v>9414</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18635,11 +18635,11 @@
         <v>1</v>
       </c>
       <c r="G527" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18669,11 +18669,11 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18703,11 +18703,11 @@
         <v>1</v>
       </c>
       <c r="G529" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19757,11 +19757,11 @@
         <v>1</v>
       </c>
       <c r="G560" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19791,11 +19791,11 @@
         <v>1</v>
       </c>
       <c r="G561" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19859,11 +19859,11 @@
         <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20301,11 +20301,11 @@
         <v>1</v>
       </c>
       <c r="G576" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20369,11 +20369,11 @@
         <v>1</v>
       </c>
       <c r="G578" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20607,7 +20607,7 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>23116</v>
+        <v>0</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20913,11 +20913,11 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20947,11 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20981,11 +20981,11 @@
         <v>1</v>
       </c>
       <c r="G596" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21015,11 +21015,11 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21083,11 +21083,11 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>734</v>
+        <v>0</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21117,11 +21117,11 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21219,7 +21219,7 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21695,11 +21695,11 @@
         <v>1</v>
       </c>
       <c r="G617" t="n">
-        <v>0</v>
+        <v>513</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21729,11 +21729,11 @@
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22137,7 +22137,7 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
@@ -22477,11 +22477,11 @@
         <v>1</v>
       </c>
       <c r="G640" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22511,11 +22511,11 @@
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22545,11 +22545,11 @@
         <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22749,11 +22749,11 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22783,11 +22783,11 @@
         <v>1</v>
       </c>
       <c r="G649" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22817,11 +22817,11 @@
         <v>1</v>
       </c>
       <c r="G650" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22851,11 +22851,11 @@
         <v>1</v>
       </c>
       <c r="G651" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23361,7 +23361,7 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
@@ -23395,11 +23395,11 @@
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23429,11 +23429,11 @@
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23463,11 +23463,11 @@
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23531,11 +23531,11 @@
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>0</v>
+        <v>1184</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23565,11 +23565,11 @@
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23633,11 +23633,11 @@
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23667,11 +23667,11 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24279,7 +24279,7 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
@@ -24685,11 +24685,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4779</v>
+        <v>6831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>be275c1c29df563c06ed80e6a3a9c98f0721dbdec0b14bf6d6fe28745737980a</t>
+          <t>332d33e747aa240334c0a3d9829224a28cb1df696189228a8ba586b2a03e6b03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -24715,11 +24715,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2738</v>
+        <v>3965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7e4b84a0c4bab1669ea097cacd283b0818ca8a4b581c079be4a9667ac12181bd</t>
+          <t>2822e25a8483d6a6d7abb92214fc02600e82eca3733e792833d60884c773daf5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -24745,11 +24745,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>185696</v>
+        <v>250495</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>118e479e2e8490ceca5cc069d46bd33c0c72e107f3de5313d16090d0297a3ab6</t>
+          <t>da1446c706063e9e318b5475b86e1e670db1f74e8f0d556266131e471fb6faf3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -24775,11 +24775,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19143</v>
+        <v>27439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2eed914ed88baf0d64420a8b2fcfe7dcc1ee775ed37e8e84042f28d44493d0ff</t>
+          <t>f547fa2319f53db81481307617a0368f3d99b6bc19775e16e61ad6e77bf18571</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -24805,11 +24805,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3171</v>
+        <v>4150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2733e78d60de6eb24e3a8870fa6f653320dd5e5fb16cd683a4ae8f9980d683b6</t>
+          <t>d07832970dd2aa449ba91b62a153411b7feee1db60ae3fb0b77ee18bc77f35cb</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -24835,11 +24835,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>391</v>
+        <v>502</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>01ae52e856921004aa85a126485c1781d9228322ba9ce6973334c542a414c047</t>
+          <t>25cb083c97c276d9285191797daedafe4d0face68ddea2be085aa808376167a9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -24865,11 +24865,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48c26f29133af66f14d8a8784e21abfb5e2d81d310bba1bfc825f320682a2120</t>
+          <t>c41051a12f01258941e4e81f969e919b5cd9720a63dea20937de7bfbedfe097f</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -24895,11 +24895,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>858</v>
+        <v>1036</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>acc49b0d55242e918b5e48deadf7c8925c9aa0eb5c41481f625fe5b9d53b5d35</t>
+          <t>c208fa680992620d481c9deeea5c61a9bbf882b78a93ca9618d118e5cdd45b1f</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -24925,11 +24925,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>279</v>
+        <v>361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>06915eacd2dd47f7dbac47fdd2fe01dc7d142d8b42aebe3aab91f0d38af6ee63</t>
+          <t>25e247e07e97cabdd880ecfa99800a9c92901eab8778be5241f11de6a72094dd</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7563</v>
+        <v>7151</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4276</v>
+        <v>4253</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>263036</v>
+        <v>239233</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28539</v>
+        <v>26834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4344</v>
+        <v>3970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1100</v>
+        <v>1026</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H757"/>
+  <dimension ref="A1:H766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2587,11 +2587,11 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1070</v>
+        <v>0</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3845,11 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3879,11 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3913,11 +3913,11 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>22276</v>
+        <v>0</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3947,11 +3947,11 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3981,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4015,11 +4015,11 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4083,11 +4083,11 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>9019</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5069,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5103,11 +5103,11 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5171,11 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>922</v>
+        <v>0</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5205,11 +5205,11 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5273,11 +5273,11 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7449,11 +7449,11 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9285,11 +9285,11 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10373,11 +10373,11 @@
         <v>1</v>
       </c>
       <c r="G284" t="n">
-        <v>0</v>
+        <v>670</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
         <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>0</v>
+        <v>941</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10815,11 +10815,11 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>9347</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11291,11 +11291,11 @@
         <v>1</v>
       </c>
       <c r="G311" t="n">
-        <v>981</v>
+        <v>0</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11325,11 +11325,11 @@
         <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11393,11 +11393,11 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>25483</v>
+        <v>0</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11903,11 +11903,11 @@
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>843</v>
+        <v>0</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11937,11 +11937,11 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12039,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12651,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12753,11 +12753,11 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12821,11 +12821,11 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>1449</v>
+        <v>0</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12957,7 +12957,7 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>1015</v>
+        <v>0</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13569,11 +13569,11 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14181,11 +14181,11 @@
         <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14487,11 +14487,11 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14521,11 +14521,11 @@
         <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14555,11 +14555,11 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14589,11 +14589,11 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14623,11 +14623,11 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>29916</v>
+        <v>0</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14793,11 +14793,11 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14827,11 +14827,11 @@
         <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14861,11 +14861,11 @@
         <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14895,11 +14895,11 @@
         <v>1</v>
       </c>
       <c r="G417" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14963,11 +14963,11 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14997,11 +14997,11 @@
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
         <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
@@ -15269,11 +15269,11 @@
         <v>1</v>
       </c>
       <c r="G428" t="n">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15303,11 +15303,11 @@
         <v>1</v>
       </c>
       <c r="G429" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15405,11 +15405,11 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15439,11 +15439,11 @@
         <v>1</v>
       </c>
       <c r="G433" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15473,11 +15473,11 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15507,11 +15507,11 @@
         <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15575,11 +15575,11 @@
         <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15711,11 +15711,11 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15745,11 +15745,11 @@
         <v>1</v>
       </c>
       <c r="G442" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15779,11 +15779,11 @@
         <v>1</v>
       </c>
       <c r="G443" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15813,11 +15813,11 @@
         <v>1</v>
       </c>
       <c r="G444" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15881,11 +15881,11 @@
         <v>1</v>
       </c>
       <c r="G446" t="n">
-        <v>1116</v>
+        <v>0</v>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15915,11 +15915,11 @@
         <v>1</v>
       </c>
       <c r="G447" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15983,11 +15983,11 @@
         <v>1</v>
       </c>
       <c r="G449" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>25022</v>
+        <v>0</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16323,11 +16323,11 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16357,11 +16357,11 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16425,11 +16425,11 @@
         <v>1</v>
       </c>
       <c r="G462" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16493,11 +16493,11 @@
         <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16629,11 +16629,11 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16663,11 +16663,11 @@
         <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16697,11 +16697,11 @@
         <v>1</v>
       </c>
       <c r="G470" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16731,11 +16731,11 @@
         <v>1</v>
       </c>
       <c r="G471" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16799,11 +16799,11 @@
         <v>1</v>
       </c>
       <c r="G473" t="n">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16833,11 +16833,11 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16935,11 +16935,11 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17547,11 +17547,11 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17581,11 +17581,11 @@
         <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17615,11 +17615,11 @@
         <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17649,11 +17649,11 @@
         <v>1</v>
       </c>
       <c r="G498" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17683,11 +17683,11 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>0</v>
+        <v>26312</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17717,11 +17717,11 @@
         <v>1</v>
       </c>
       <c r="G500" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17751,11 +17751,11 @@
         <v>1</v>
       </c>
       <c r="G501" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17785,11 +17785,11 @@
         <v>1</v>
       </c>
       <c r="G502" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18261,11 +18261,11 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18329,11 +18329,11 @@
         <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>839</v>
+        <v>0</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18363,11 +18363,11 @@
         <v>1</v>
       </c>
       <c r="G519" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18397,11 +18397,11 @@
         <v>1</v>
       </c>
       <c r="G520" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18431,11 +18431,11 @@
         <v>1</v>
       </c>
       <c r="G521" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18465,11 +18465,11 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18499,11 +18499,11 @@
         <v>1</v>
       </c>
       <c r="G523" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>0</v>
+        <v>9414</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18635,11 +18635,11 @@
         <v>1</v>
       </c>
       <c r="G527" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18669,11 +18669,11 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18703,11 +18703,11 @@
         <v>1</v>
       </c>
       <c r="G529" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18771,11 +18771,11 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18805,11 +18805,11 @@
         <v>1</v>
       </c>
       <c r="G532" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18839,11 +18839,11 @@
         <v>1</v>
       </c>
       <c r="G533" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18873,11 +18873,11 @@
         <v>1</v>
       </c>
       <c r="G534" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18941,11 +18941,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="n">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18975,11 +18975,11 @@
         <v>1</v>
       </c>
       <c r="G537" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19689,11 +19689,11 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19757,11 +19757,11 @@
         <v>1</v>
       </c>
       <c r="G560" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19791,11 +19791,11 @@
         <v>1</v>
       </c>
       <c r="G561" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20029,11 +20029,11 @@
         <v>1</v>
       </c>
       <c r="G568" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20063,11 +20063,11 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20097,11 +20097,11 @@
         <v>1</v>
       </c>
       <c r="G570" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20165,11 +20165,11 @@
         <v>1</v>
       </c>
       <c r="G572" t="n">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20199,11 +20199,11 @@
         <v>1</v>
       </c>
       <c r="G573" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20301,7 +20301,7 @@
         <v>1</v>
       </c>
       <c r="G576" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>0</v>
+        <v>23116</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20913,11 +20913,11 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20947,11 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20981,11 +20981,11 @@
         <v>1</v>
       </c>
       <c r="G596" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21015,11 +21015,11 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21219,11 +21219,11 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21253,11 +21253,11 @@
         <v>1</v>
       </c>
       <c r="G604" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21287,11 +21287,11 @@
         <v>1</v>
       </c>
       <c r="G605" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21321,11 +21321,11 @@
         <v>1</v>
       </c>
       <c r="G606" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21831,11 +21831,11 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         <v>1</v>
       </c>
       <c r="G622" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21899,11 +21899,11 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21933,11 +21933,11 @@
         <v>1</v>
       </c>
       <c r="G624" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22001,11 +22001,11 @@
         <v>1</v>
       </c>
       <c r="G626" t="n">
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22137,7 +22137,7 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
@@ -22545,11 +22545,11 @@
         <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>803</v>
+        <v>0</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22749,11 +22749,11 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22783,11 +22783,11 @@
         <v>1</v>
       </c>
       <c r="G649" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22817,11 +22817,11 @@
         <v>1</v>
       </c>
       <c r="G650" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22851,11 +22851,11 @@
         <v>1</v>
       </c>
       <c r="G651" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23089,11 +23089,11 @@
         <v>1</v>
       </c>
       <c r="G658" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23191,11 +23191,11 @@
         <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>0</v>
+        <v>11063</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23225,11 +23225,11 @@
         <v>1</v>
       </c>
       <c r="G662" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23259,11 +23259,11 @@
         <v>1</v>
       </c>
       <c r="G663" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23293,11 +23293,11 @@
         <v>1</v>
       </c>
       <c r="G664" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23361,7 +23361,7 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
@@ -23701,11 +23701,11 @@
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23735,11 +23735,11 @@
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23769,11 +23769,11 @@
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23803,11 +23803,11 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>0</v>
+        <v>30616</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24279,11 +24279,11 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24619,11 +24619,11 @@
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24653,11 +24653,11 @@
         <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24687,11 +24687,11 @@
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24755,11 +24755,11 @@
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>0</v>
+        <v>617</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24891,7 +24891,7 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
@@ -25333,11 +25333,11 @@
         <v>1</v>
       </c>
       <c r="G724" t="n">
-        <v>21955</v>
+        <v>0</v>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25367,11 +25367,11 @@
         <v>1</v>
       </c>
       <c r="G725" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25401,11 +25401,11 @@
         <v>1</v>
       </c>
       <c r="G726" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25435,11 +25435,11 @@
         <v>1</v>
       </c>
       <c r="G727" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25503,11 +25503,11 @@
         <v>1</v>
       </c>
       <c r="G729" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25537,11 +25537,11 @@
         <v>1</v>
       </c>
       <c r="G730" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25571,11 +25571,11 @@
         <v>1</v>
       </c>
       <c r="G731" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25809,11 +25809,11 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26013,11 +26013,11 @@
         <v>1</v>
       </c>
       <c r="G744" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26115,7 +26115,7 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
@@ -26460,6 +26460,312 @@
       <c r="H757" t="inlineStr">
         <is>
           <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>1294</v>
+      </c>
+      <c r="C758" t="n">
+        <v>11365</v>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F758" t="b">
+        <v>1</v>
+      </c>
+      <c r="G758" t="n">
+        <v>78</v>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>race_control</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>1294</v>
+      </c>
+      <c r="C759" t="n">
+        <v>11365</v>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F759" t="b">
+        <v>1</v>
+      </c>
+      <c r="G759" t="n">
+        <v>141</v>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>intervals</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>1294</v>
+      </c>
+      <c r="C760" t="n">
+        <v>11365</v>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F760" t="b">
+        <v>1</v>
+      </c>
+      <c r="G760" t="n">
+        <v>0</v>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>1294</v>
+      </c>
+      <c r="C761" t="n">
+        <v>11365</v>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F761" t="b">
+        <v>1</v>
+      </c>
+      <c r="G761" t="n">
+        <v>953</v>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>stints</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>1294</v>
+      </c>
+      <c r="C762" t="n">
+        <v>11365</v>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F762" t="b">
+        <v>1</v>
+      </c>
+      <c r="G762" t="n">
+        <v>0</v>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>pit</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>1294</v>
+      </c>
+      <c r="C763" t="n">
+        <v>11365</v>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F763" t="b">
+        <v>0</v>
+      </c>
+      <c r="G763" t="n">
+        <v>0</v>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>skipped_not_applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>starting_grid</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>1294</v>
+      </c>
+      <c r="C764" t="n">
+        <v>11365</v>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F764" t="b">
+        <v>1</v>
+      </c>
+      <c r="G764" t="n">
+        <v>0</v>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>drivers</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>1294</v>
+      </c>
+      <c r="C765" t="n">
+        <v>11365</v>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F765" t="b">
+        <v>1</v>
+      </c>
+      <c r="G765" t="n">
+        <v>0</v>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>team_radio</t>
+        </is>
+      </c>
+      <c r="B766" t="n">
+        <v>1294</v>
+      </c>
+      <c r="C766" t="n">
+        <v>11365</v>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F766" t="b">
+        <v>1</v>
+      </c>
+      <c r="G766" t="n">
+        <v>0</v>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26521,11 +26827,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7563</v>
+        <v>7151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>d314ecd63c2d8ac15adedeadf35d4aff75c073b5518b8bf736ac991e989b779f</t>
+          <t>696f8f5189a179d479cb6730b91bc40d52dbe442b0b658b44557d7e072962f92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -26551,11 +26857,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4276</v>
+        <v>4253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7ffd36283c3e12ee9f14109c69413148fb08a2dd5fff1293f675242d446ff442</t>
+          <t>bd7351c72dccf12656aaaac1bba09d4944396abb2ab2bf988d0ead837caf9ec8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -26581,11 +26887,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>263036</v>
+        <v>239233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>71d148af89f02b5624cc46ed98758bcfa50c1ec4ec793826de86f6171408d25a</t>
+          <t>b15452b2df8a96fbb915b3a40ed64c1862963e52c8abbe651f9013fecefd266a</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -26611,11 +26917,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28539</v>
+        <v>26834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>029e35e624851844597e2cd7508eed5b6c00a29e4b4f6a8f95ec93047b762959</t>
+          <t>003044004d9e77e9faf9cd1c10a54edc16e6ada75cf5c67b5ea29032de05fe30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -26641,11 +26947,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4344</v>
+        <v>3970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19de38438cac0850acd3700590d15dc3209f4ba16309a020bc002911708dbc71</t>
+          <t>9d764d027ac669206e3b3c79f1189be67dfa68a46c8e9a0ebb9b1c65f1c64847</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -26671,11 +26977,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>96bdf58bc0732b46da68a933b75ce3770284ca6f190e5189ea92db6d37b0cb78</t>
+          <t>6f7220fbf5ea15322b766b65aae65e996de7ac305ff5c32c1aa269eaeab1a726</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -26701,11 +27007,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4f4b30d5468cbef1c869bf91842313bbc2f42504ff6d34aa6c2ec743018c5ef7</t>
+          <t>7b907b1636be5a298ebaada02d0e618c0a5dc2c740cb1fd99db41510b36ae13a</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -26731,11 +27037,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1100</v>
+        <v>1026</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>d8488e49e890eae34a3639537f1bbd568985586f27a84a87a29288eab84e40bc</t>
+          <t>0f4e318f1693c97045e186e5e4c62f15cb0f4e6497330fddabb8c5b8c3d172a0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -26761,11 +27067,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>acee90ccce96c308ea8310a67c15435e41d0061980e0ed4a088ad63359fe4935</t>
+          <t>0a0dff83a3f0d398af1aeb9949eb42622daff0c73049d1c779ad493bb6afbd59</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -26790,7 +27096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P85"/>
+  <dimension ref="A1:P86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32587,6 +32893,74 @@
         <v>1</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>11365</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-09-12T14:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-09-12T15:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1294</v>
+      </c>
+      <c r="G86" t="n">
+        <v>153</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Madring</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O86" t="b">
+        <v>0</v>
+      </c>
+      <c r="P86" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
